--- a/diseases/d127/2000-2004.xlsx
+++ b/diseases/d127/2000-2004.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -765,34 +765,17 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -800,135 +783,72 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -960,12 +880,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -990,12 +910,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1006,22 +926,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Viral Haemorrhagic Fever</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1031,7 +951,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1046,7 +966,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1071,7 +991,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1081,12 +1001,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1095,7 +1015,7 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1104,70 +1024,65 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1144,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1388,12 +1303,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1587,17 +1502,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1622,12 +1537,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1636,34 +1551,12 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1671,64 +1564,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1736,70 +1571,55 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1681,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -2020,12 +1840,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2219,17 +2039,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2254,12 +2074,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2268,34 +2088,12 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2303,64 +2101,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>0</v>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2368,1486 +2108,53 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2003-01-01</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2003-01</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2003-01-01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2003-01</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Other Viral Haemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:PL:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Viral Haemorrhagic Fever</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2004-01</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Other Viral Haemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>country:PL:national</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -3898,7 +2205,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
     </row>
@@ -3979,7 +2286,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -3999,7 +2306,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4009,7 +2316,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2000-2004.xlsx
+++ b/diseases/d127/2000-2004.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -765,17 +765,34 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -783,6 +800,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -790,65 +865,70 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -880,12 +960,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -910,12 +990,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -926,22 +1006,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Viral Haemorrhagic Fever</t>
+          <t>Blæðandi veiruhitasóttir</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -951,7 +1031,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -966,7 +1046,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -991,7 +1071,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1001,12 +1081,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>IS_DOH_historical_registry_annual</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1015,7 +1095,7 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1024,65 +1104,70 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1229,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1303,12 +1388,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1502,17 +1587,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1537,12 +1622,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1551,12 +1636,34 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1564,6 +1671,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1571,55 +1736,70 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1861,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1840,12 +2020,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2039,122 +2219,1635 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2003-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>D127</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Viral hemorrhagic fevers</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>病毒性出血热</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2003-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2003-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2004-01</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT15" t="n">
         <v>1</v>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -2205,7 +3898,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
     </row>
@@ -2286,7 +3979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -2306,7 +3999,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2316,7 +4009,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
